--- a/Output/Models/Exposure_models_malf_card_bin_iqr_Masculino.xlsx
+++ b/Output/Models/Exposure_models_malf_card_bin_iqr_Masculino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6757687853404737</v>
+        <v>0.6597355873792951</v>
       </c>
       <c r="C3">
-        <v>0.2454653509549624</v>
+        <v>0.2450248548381354</v>
       </c>
       <c r="D3">
-        <v>-1.596576842480281</v>
+        <v>-1.69744473347823</v>
       </c>
       <c r="E3">
-        <v>0.1103600643243769</v>
+        <v>0.08961261136403219</v>
       </c>
       <c r="F3">
-        <v>0.417693427621073</v>
+        <v>0.4081355047565255</v>
       </c>
       <c r="G3">
-        <v>1.09329814893525</v>
+        <v>1.066437592863561</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8365917436868237</v>
+        <v>0.9975327821997713</v>
       </c>
       <c r="C4">
-        <v>0.2401023630341722</v>
+        <v>0.2311476107699222</v>
       </c>
       <c r="D4">
-        <v>-0.7430959306598214</v>
+        <v>-0.01068696487598864</v>
       </c>
       <c r="E4">
-        <v>0.4574236031740442</v>
+        <v>0.9914731980333219</v>
       </c>
       <c r="F4">
-        <v>0.5225622972507125</v>
+        <v>0.6341236838598908</v>
       </c>
       <c r="G4">
-        <v>1.339334562189381</v>
+        <v>1.569207517224789</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.70005585883254</v>
+        <v>1.708196869346776</v>
       </c>
       <c r="C5">
-        <v>0.22780857945931</v>
+        <v>0.2250647927205151</v>
       </c>
       <c r="D5">
-        <v>2.329416696766356</v>
+        <v>2.37904092121862</v>
       </c>
       <c r="E5">
-        <v>0.01983700138496497</v>
+        <v>0.01735774892096106</v>
       </c>
       <c r="F5">
-        <v>1.087807820812924</v>
+        <v>1.098910752148189</v>
       </c>
       <c r="G5">
-        <v>2.656893862916883</v>
+        <v>2.655298930092406</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="6">
@@ -812,26 +812,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B8">
-        <v>1.135334609184092</v>
+        <v>1.200832516549209</v>
       </c>
       <c r="C8">
-        <v>0.2453301897898023</v>
+        <v>0.3537385795938811</v>
       </c>
       <c r="D8">
-        <v>0.5173738195370761</v>
+        <v>0.5173738195370868</v>
       </c>
       <c r="E8">
-        <v>0.6048952318294211</v>
+        <v>0.6048952318294135</v>
       </c>
       <c r="F8">
-        <v>0.7019374938859837</v>
+        <v>0.6003155796800661</v>
       </c>
       <c r="G8">
-        <v>1.836324011808046</v>
+        <v>2.402067815015577</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,26 +875,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.6318123311056284</v>
+        <v>0.4960087390937506</v>
       </c>
       <c r="C9">
-        <v>0.2644874329209376</v>
+        <v>0.3828582140758549</v>
       </c>
       <c r="D9">
-        <v>-1.736047978969153</v>
+        <v>-1.831387462756327</v>
       </c>
       <c r="E9">
-        <v>0.08255535141343689</v>
+        <v>0.06704273126398977</v>
       </c>
       <c r="F9">
-        <v>0.376232221345396</v>
+        <v>0.2342069754634483</v>
       </c>
       <c r="G9">
-        <v>1.061011787639153</v>
+        <v>1.05045833400367</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -938,26 +938,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.7797468099563873</v>
+        <v>0.9231362957720682</v>
       </c>
       <c r="C10">
-        <v>0.2609247711732547</v>
+        <v>0.3719789635221135</v>
       </c>
       <c r="D10">
-        <v>-0.953477944982676</v>
+        <v>-0.2150078288432857</v>
       </c>
       <c r="E10">
-        <v>0.3403479655845383</v>
+        <v>0.8297612147684695</v>
       </c>
       <c r="F10">
-        <v>0.4675779674862126</v>
+        <v>0.4452836603824717</v>
       </c>
       <c r="G10">
-        <v>1.300328779189303</v>
+        <v>1.913792704272606</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1001,26 +1001,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B11">
-        <v>1.644061259788025</v>
+        <v>2.08339977080319</v>
       </c>
       <c r="C11">
-        <v>0.2455631075007233</v>
+        <v>0.3596144002085212</v>
       </c>
       <c r="D11">
-        <v>2.024610144596223</v>
+        <v>2.041078066205494</v>
       </c>
       <c r="E11">
-        <v>0.04290741174984433</v>
+        <v>0.0412430681563066</v>
       </c>
       <c r="F11">
-        <v>1.016001384600757</v>
+        <v>1.029599397196972</v>
       </c>
       <c r="G11">
-        <v>2.660367856681535</v>
+        <v>4.215770344077226</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,32 +1058,32 @@
         </is>
       </c>
       <c r="O11">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.8607198426260104</v>
+        <v>0.8122826592382248</v>
       </c>
       <c r="C12">
-        <v>0.2075082615766399</v>
+        <v>0.2876424287603134</v>
       </c>
       <c r="D12">
-        <v>-0.7227963474651389</v>
+        <v>-0.7227963474651249</v>
       </c>
       <c r="E12">
-        <v>0.4698050116806466</v>
+        <v>0.4698050116806553</v>
       </c>
       <c r="F12">
-        <v>0.5731000714674535</v>
+        <v>0.4622378480857103</v>
       </c>
       <c r="G12">
-        <v>1.292686363819825</v>
+        <v>1.427410414858063</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1127,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.9818356872504987</v>
+        <v>0.9202151061838517</v>
       </c>
       <c r="C13">
-        <v>0.2237112477010848</v>
+        <v>1.014717688493434</v>
       </c>
       <c r="D13">
-        <v>-0.08194183085799203</v>
+        <v>-0.08194183085804486</v>
       </c>
       <c r="E13">
-        <v>0.9346929700517804</v>
+        <v>0.9346929700517383</v>
       </c>
       <c r="F13">
-        <v>0.6333087002141718</v>
+        <v>0.1259389580774367</v>
       </c>
       <c r="G13">
-        <v>1.522166546003006</v>
+        <v>6.723859356755072</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1190,26 +1190,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B14">
-        <v>1.098362734750462</v>
+        <v>1.142474624140768</v>
       </c>
       <c r="C14">
-        <v>0.2317389683403116</v>
+        <v>0.3289984762996792</v>
       </c>
       <c r="D14">
-        <v>0.4048548620040306</v>
+        <v>0.4048548620040522</v>
       </c>
       <c r="E14">
-        <v>0.685584199140959</v>
+        <v>0.6855841991409433</v>
       </c>
       <c r="F14">
-        <v>0.6974116892385269</v>
+        <v>0.5995184485297896</v>
       </c>
       <c r="G14">
-        <v>1.729825748125513</v>
+        <v>2.177161136586327</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1253,26 +1253,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.6469877512904187</v>
+        <v>0.513260288721941</v>
       </c>
       <c r="C15">
-        <v>0.2504550682404995</v>
+        <v>0.3605808569525368</v>
       </c>
       <c r="D15">
-        <v>-1.738547034661197</v>
+        <v>-1.849715990754145</v>
       </c>
       <c r="E15">
-        <v>0.08211446993839004</v>
+        <v>0.06435449452754576</v>
       </c>
       <c r="F15">
-        <v>0.3960119744390865</v>
+        <v>0.2531690908523775</v>
       </c>
       <c r="G15">
-        <v>1.057021447173991</v>
+        <v>1.040554054572718</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1316,26 +1316,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.7922755872556724</v>
+        <v>0.9494801295833923</v>
       </c>
       <c r="C16">
-        <v>0.2468589493835706</v>
+        <v>0.344910790447081</v>
       </c>
       <c r="D16">
-        <v>-0.9432349305861606</v>
+        <v>-0.1503016943132554</v>
       </c>
       <c r="E16">
-        <v>0.3455607502195913</v>
+        <v>0.8805265963071753</v>
       </c>
       <c r="F16">
-        <v>0.4883706493635702</v>
+        <v>0.4829445653991498</v>
       </c>
       <c r="G16">
-        <v>1.285295516795125</v>
+        <v>1.866699785157749</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1379,26 +1379,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B17">
-        <v>1.66293730156315</v>
+        <v>2.064751828283572</v>
       </c>
       <c r="C17">
-        <v>0.2271271084365711</v>
+        <v>0.3312304636586827</v>
       </c>
       <c r="D17">
-        <v>2.239210902627936</v>
+        <v>2.188838644774936</v>
       </c>
       <c r="E17">
-        <v>0.02514219678918345</v>
+        <v>0.02860856982370596</v>
       </c>
       <c r="F17">
-        <v>1.065479087091828</v>
+        <v>1.078757871035127</v>
       </c>
       <c r="G17">
-        <v>2.595415060166074</v>
+        <v>3.951952729030456</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1436,32 +1436,32 @@
         </is>
       </c>
       <c r="O17">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.8658080426384445</v>
+        <v>0.8175480231576308</v>
       </c>
       <c r="C18">
-        <v>0.1893241385215168</v>
+        <v>0.2646816382877627</v>
       </c>
       <c r="D18">
-        <v>-0.7610865465226083</v>
+        <v>-0.7610865465226028</v>
       </c>
       <c r="E18">
-        <v>0.4466053755439927</v>
+        <v>0.4466053755439958</v>
       </c>
       <c r="F18">
-        <v>0.5974046749918098</v>
+        <v>0.4866490207074934</v>
       </c>
       <c r="G18">
-        <v>1.254800302169867</v>
+        <v>1.373443162789577</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1505,26 +1505,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B19">
-        <v>1.007863985479821</v>
+        <v>1.034387246915991</v>
       </c>
       <c r="C19">
-        <v>0.211928534067865</v>
+        <v>0.9147110992588229</v>
       </c>
       <c r="D19">
-        <v>0.03696163680468462</v>
+        <v>0.03696163680464537</v>
       </c>
       <c r="E19">
-        <v>0.9705155942197317</v>
+        <v>0.970515594219763</v>
       </c>
       <c r="F19">
-        <v>0.6652854591423408</v>
+        <v>0.1722184428523141</v>
       </c>
       <c r="G19">
-        <v>1.526848060886202</v>
+        <v>6.212789750398485</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.7396959880975608</v>
+        <v>0.7231047111932497</v>
       </c>
       <c r="C21">
-        <v>0.2190315502669383</v>
+        <v>0.2200672472334774</v>
       </c>
       <c r="D21">
-        <v>-1.376587088591278</v>
+        <v>-1.473191684023776</v>
       </c>
       <c r="E21">
-        <v>0.1686399449949727</v>
+        <v>0.1406993567909525</v>
       </c>
       <c r="F21">
-        <v>0.4815188239609918</v>
+        <v>0.4697638688142247</v>
       </c>
       <c r="G21">
-        <v>1.136300654472341</v>
+        <v>1.113070753333424</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.8660211519339673</v>
+        <v>1.01180165963519</v>
       </c>
       <c r="C22">
-        <v>0.212872870224137</v>
+        <v>0.2062766932758203</v>
       </c>
       <c r="D22">
-        <v>-0.6757363946871836</v>
+        <v>0.05687779345266505</v>
       </c>
       <c r="E22">
-        <v>0.4992080243902902</v>
+        <v>0.9546425439278566</v>
       </c>
       <c r="F22">
-        <v>0.5705987078354184</v>
+        <v>0.6753242544326695</v>
       </c>
       <c r="G22">
-        <v>1.314395958662705</v>
+        <v>1.515927484791076</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.521820296783936</v>
+        <v>1.519638568468469</v>
       </c>
       <c r="C23">
-        <v>0.1810644739424939</v>
+        <v>0.1787731094458511</v>
       </c>
       <c r="D23">
-        <v>2.3191030956067</v>
+        <v>2.34080239459917</v>
       </c>
       <c r="E23">
-        <v>0.02038944696431578</v>
+        <v>0.01924234860407487</v>
       </c>
       <c r="F23">
-        <v>1.067188194739699</v>
+        <v>1.070454866225473</v>
       </c>
       <c r="G23">
-        <v>2.170129905033699</v>
+        <v>2.157308497199622</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="24">
@@ -1946,26 +1946,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B26">
-        <v>1.185580764364957</v>
+        <v>1.272247658056425</v>
       </c>
       <c r="C26">
-        <v>0.2341368017359712</v>
+        <v>0.331174016601344</v>
       </c>
       <c r="D26">
-        <v>0.7270653300863946</v>
+        <v>0.7270653300863894</v>
       </c>
       <c r="E26">
-        <v>0.4671859359959868</v>
+        <v>0.46718593599599</v>
       </c>
       <c r="F26">
-        <v>0.7492617070979879</v>
+        <v>0.6647767563279041</v>
       </c>
       <c r="G26">
-        <v>1.875982364394836</v>
+        <v>2.43482355245235</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2009,26 +2009,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.6762471629904574</v>
+        <v>0.5503991997630947</v>
       </c>
       <c r="C27">
-        <v>0.2496031718515981</v>
+        <v>0.3592314610801869</v>
       </c>
       <c r="D27">
-        <v>-1.567274330436107</v>
+        <v>-1.662191402967264</v>
       </c>
       <c r="E27">
-        <v>0.1170505827560294</v>
+        <v>0.09647440322880163</v>
       </c>
       <c r="F27">
-        <v>0.4146129389084789</v>
+        <v>0.2722070818245373</v>
       </c>
       <c r="G27">
-        <v>1.102981075932095</v>
+        <v>1.112900065161154</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2072,26 +2072,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.8259304529997459</v>
+        <v>0.9958971401009168</v>
       </c>
       <c r="C28">
-        <v>0.2460747497164592</v>
+        <v>0.3454791611519717</v>
       </c>
       <c r="D28">
-        <v>-0.7771813506391282</v>
+        <v>-0.01190028280692808</v>
       </c>
       <c r="E28">
-        <v>0.4370517834646878</v>
+        <v>0.9905051721841058</v>
       </c>
       <c r="F28">
-        <v>0.5098991319618863</v>
+        <v>0.5059901820285319</v>
       </c>
       <c r="G28">
-        <v>1.337835407892703</v>
+        <v>1.960139047925753</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2135,26 +2135,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B29">
-        <v>1.637397877209132</v>
+        <v>2.045435355807483</v>
       </c>
       <c r="C29">
-        <v>0.229634890892916</v>
+        <v>0.3322437484484259</v>
       </c>
       <c r="D29">
-        <v>2.147358006450818</v>
+        <v>2.153872444868139</v>
       </c>
       <c r="E29">
-        <v>0.03176479111146265</v>
+        <v>0.03125017643453058</v>
       </c>
       <c r="F29">
-        <v>1.04397151622145</v>
+        <v>1.066545449637673</v>
       </c>
       <c r="G29">
-        <v>2.568146512265817</v>
+        <v>3.922763719266356</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2192,32 +2192,32 @@
         </is>
       </c>
       <c r="O29">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.8751706062360769</v>
+        <v>0.8391310914611979</v>
       </c>
       <c r="C30">
-        <v>0.2057653960924503</v>
+        <v>0.2706600881154597</v>
       </c>
       <c r="D30">
-        <v>-0.6480022180937862</v>
+        <v>-0.6480022180937826</v>
       </c>
       <c r="E30">
-        <v>0.5169835156545626</v>
+        <v>0.5169835156545649</v>
       </c>
       <c r="F30">
-        <v>0.5847158953556262</v>
+        <v>0.49367772056736</v>
       </c>
       <c r="G30">
-        <v>1.309907249150094</v>
+        <v>1.426317128201828</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2261,14 +2261,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B31">
-        <v>1.074983086667119</v>
+        <v>1.369242343718138</v>
       </c>
       <c r="C31">
-        <v>0.1957522983363077</v>
+        <v>0.85079454307701</v>
       </c>
       <c r="D31">
         <v>0.3693694977655968</v>
@@ -2277,10 +2277,10 @@
         <v>0.7118523302646829</v>
       </c>
       <c r="F31">
-        <v>0.7324482958099805</v>
+        <v>0.2583941595742176</v>
       </c>
       <c r="G31">
-        <v>1.577706772247254</v>
+        <v>7.255677136511437</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2324,26 +2324,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B32">
-        <v>1.147286468178511</v>
+        <v>1.156292969943186</v>
       </c>
       <c r="C32">
-        <v>0.206711918255523</v>
+        <v>0.2184761975083296</v>
       </c>
       <c r="D32">
-        <v>0.6646910464584261</v>
+        <v>0.6646910464584298</v>
       </c>
       <c r="E32">
-        <v>0.5062481217271065</v>
+        <v>0.5062481217271042</v>
       </c>
       <c r="F32">
-        <v>0.7651002915406534</v>
+        <v>0.7535301064438346</v>
       </c>
       <c r="G32">
-        <v>1.720383921714376</v>
+        <v>1.774333130032263</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2387,26 +2387,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.6989739840806923</v>
+        <v>0.6641237390903753</v>
       </c>
       <c r="C33">
-        <v>0.2326414631184612</v>
+        <v>0.2478052632683116</v>
       </c>
       <c r="D33">
-        <v>-1.539457977133151</v>
+        <v>-1.651646891666448</v>
       </c>
       <c r="E33">
-        <v>0.1236925293981809</v>
+        <v>0.09860655495855553</v>
       </c>
       <c r="F33">
-        <v>0.443033165862525</v>
+        <v>0.4086173301548712</v>
       </c>
       <c r="G33">
-        <v>1.102772135513754</v>
+        <v>1.07939705018437</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,26 +2450,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.8143874936838644</v>
+        <v>0.9802820255169817</v>
       </c>
       <c r="C34">
-        <v>0.2269788729784028</v>
+        <v>0.230315727382142</v>
       </c>
       <c r="D34">
-        <v>-0.9045731309181468</v>
+        <v>-0.08646811837451496</v>
       </c>
       <c r="E34">
-        <v>0.3656915752226085</v>
+        <v>0.9310942989762877</v>
       </c>
       <c r="F34">
-        <v>0.521946907484809</v>
+        <v>0.6241743776305593</v>
       </c>
       <c r="G34">
-        <v>1.270679029529434</v>
+        <v>1.539558309329468</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2513,26 +2513,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B35">
-        <v>1.58868414473934</v>
+        <v>1.636454982747344</v>
       </c>
       <c r="C35">
-        <v>0.1924246157535369</v>
+        <v>0.209099687101535</v>
       </c>
       <c r="D35">
-        <v>2.405649037465805</v>
+        <v>2.355490403439192</v>
       </c>
       <c r="E35">
-        <v>0.01614376552498634</v>
+        <v>0.01849827483610626</v>
       </c>
       <c r="F35">
-        <v>1.089545650629176</v>
+        <v>1.086220729036118</v>
       </c>
       <c r="G35">
-        <v>2.316486060302927</v>
+        <v>2.465415029351334</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2570,32 +2570,32 @@
         </is>
       </c>
       <c r="O35">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.8680124679436158</v>
+        <v>0.8654661348723728</v>
       </c>
       <c r="C36">
-        <v>0.1797785418934447</v>
+        <v>0.183509818682368</v>
       </c>
       <c r="D36">
-        <v>-0.7873531453965397</v>
+        <v>-0.7873531453965489</v>
       </c>
       <c r="E36">
-        <v>0.4310751668706387</v>
+        <v>0.4310751668706333</v>
       </c>
       <c r="F36">
-        <v>0.6102365148263028</v>
+        <v>0.604012933390963</v>
       </c>
       <c r="G36">
-        <v>1.234678073500775</v>
+        <v>1.240092039761165</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,26 +2639,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B37">
-        <v>1.070840326433901</v>
+        <v>1.211151703765692</v>
       </c>
       <c r="C37">
-        <v>0.1734786011695673</v>
+        <v>0.4855611150697893</v>
       </c>
       <c r="D37">
-        <v>0.3945367993078019</v>
+        <v>0.3945367993077887</v>
       </c>
       <c r="E37">
-        <v>0.6931847639443953</v>
+        <v>0.6931847639444051</v>
       </c>
       <c r="F37">
-        <v>0.7621833630442081</v>
+        <v>0.4676147201685363</v>
       </c>
       <c r="G37">
-        <v>1.504492305023658</v>
+        <v>3.136959523014687</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.805696743433638</v>
+        <v>0.7642918149826525</v>
       </c>
       <c r="C39">
-        <v>0.5625171759282215</v>
+        <v>0.5487210565190436</v>
       </c>
       <c r="D39">
-        <v>-0.3840733498670482</v>
+        <v>-0.4898766008073427</v>
       </c>
       <c r="E39">
-        <v>0.7009240832219221</v>
+        <v>0.6242212217962939</v>
       </c>
       <c r="F39">
-        <v>0.2675199163905967</v>
+        <v>0.2607275949253554</v>
       </c>
       <c r="G39">
-        <v>2.426537998134582</v>
+        <v>2.240430203088834</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.9310925632866556</v>
+        <v>1.468387005001148</v>
       </c>
       <c r="C40">
-        <v>0.5744408029398275</v>
+        <v>0.5679098188815856</v>
       </c>
       <c r="D40">
-        <v>-0.1242888436425681</v>
+        <v>0.6764533911216126</v>
       </c>
       <c r="E40">
-        <v>0.9010865802922559</v>
+        <v>0.4987528287290113</v>
       </c>
       <c r="F40">
-        <v>0.3020146151774803</v>
+        <v>0.482430568209877</v>
       </c>
       <c r="G40">
-        <v>2.870501352718501</v>
+        <v>4.469369352893544</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>2.222130036973835</v>
+        <v>1.584306217254778</v>
       </c>
       <c r="C41">
-        <v>0.5237272019967054</v>
+        <v>0.4765165055338043</v>
       </c>
       <c r="D41">
-        <v>1.524584189920618</v>
+        <v>0.9656467054945748</v>
       </c>
       <c r="E41">
-        <v>0.1273628432640794</v>
+        <v>0.3342209959090814</v>
       </c>
       <c r="F41">
-        <v>0.796108145136343</v>
+        <v>0.6226264148459766</v>
       </c>
       <c r="G41">
-        <v>6.202501420677801</v>
+        <v>4.031351915342474</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="42">
@@ -3080,26 +3080,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.494731199959222</v>
+        <v>0.3625057143660499</v>
       </c>
       <c r="C44">
-        <v>0.6293920392552972</v>
+        <v>0.9075126308939869</v>
       </c>
       <c r="D44">
-        <v>-1.11812773343293</v>
+        <v>-1.118127733432921</v>
       </c>
       <c r="E44">
-        <v>0.2635124431990071</v>
+        <v>0.2635124431990107</v>
       </c>
       <c r="F44">
-        <v>0.1440886673534059</v>
+        <v>0.061212300988879</v>
       </c>
       <c r="G44">
-        <v>1.698669053637452</v>
+        <v>2.146797144121648</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3143,26 +3143,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B45">
-        <v>0.7934086620305062</v>
+        <v>0.6650213364675784</v>
       </c>
       <c r="C45">
-        <v>0.6098930455061088</v>
+        <v>0.8537290577035732</v>
       </c>
       <c r="D45">
-        <v>-0.379438419667607</v>
+        <v>-0.477828592392813</v>
       </c>
       <c r="E45">
-        <v>0.7043623250504549</v>
+        <v>0.6327722088148802</v>
       </c>
       <c r="F45">
-        <v>0.2400794768382813</v>
+        <v>0.124778594076452</v>
       </c>
       <c r="G45">
-        <v>2.62203714068017</v>
+        <v>3.544304864391685</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3206,26 +3206,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B46">
-        <v>0.7849283152390404</v>
+        <v>1.616728754240337</v>
       </c>
       <c r="C46">
-        <v>0.6242792628490036</v>
+        <v>0.8898683738480989</v>
       </c>
       <c r="D46">
-        <v>-0.3879079411210341</v>
+        <v>0.5398605393190332</v>
       </c>
       <c r="E46">
-        <v>0.6980841612337403</v>
+        <v>0.5892932131592457</v>
       </c>
       <c r="F46">
-        <v>0.2309098844878156</v>
+        <v>0.2826049922400135</v>
       </c>
       <c r="G46">
-        <v>2.668194397267166</v>
+        <v>9.248993954670233</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3269,26 +3269,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B47">
-        <v>2.303928562752607</v>
+        <v>1.703564117518502</v>
       </c>
       <c r="C47">
-        <v>0.5776888157063115</v>
+        <v>0.7675288788528472</v>
       </c>
       <c r="D47">
-        <v>1.444749688606619</v>
+        <v>0.694074986341488</v>
       </c>
       <c r="E47">
-        <v>0.1485282074977465</v>
+        <v>0.4876351843326577</v>
       </c>
       <c r="F47">
-        <v>0.7425734159798348</v>
+        <v>0.3784745817644249</v>
       </c>
       <c r="G47">
-        <v>7.148231687318359</v>
+        <v>7.667967262073558</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,32 +3326,32 @@
         </is>
       </c>
       <c r="O47">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B48">
-        <v>0.7354671892562745</v>
+        <v>0.6531810882883298</v>
       </c>
       <c r="C48">
-        <v>0.3756265977274352</v>
+        <v>0.5206835913730019</v>
       </c>
       <c r="D48">
-        <v>-0.8179648403899427</v>
+        <v>-0.8179648403899141</v>
       </c>
       <c r="E48">
-        <v>0.4133772639564537</v>
+        <v>0.4133772639564701</v>
       </c>
       <c r="F48">
-        <v>0.3522324495689748</v>
+        <v>0.2354110939602336</v>
       </c>
       <c r="G48">
-        <v>1.535667673817209</v>
+        <v>1.812342515045604</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,26 +3395,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.533643195177997</v>
+        <v>6.956891688157793</v>
       </c>
       <c r="C49">
-        <v>0.4925840345786834</v>
+        <v>2.234280744007609</v>
       </c>
       <c r="D49">
-        <v>0.868168775685691</v>
+        <v>0.8681687756857553</v>
       </c>
       <c r="E49">
-        <v>0.3853019449370373</v>
+        <v>0.385301944937002</v>
       </c>
       <c r="F49">
-        <v>0.5840311906626633</v>
+        <v>0.08721516858406426</v>
       </c>
       <c r="G49">
-        <v>4.027287391015948</v>
+        <v>554.9303263010856</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3458,26 +3458,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B50">
-        <v>0.4966516945622958</v>
+        <v>0.3702428384523355</v>
       </c>
       <c r="C50">
-        <v>0.5772217597124903</v>
+        <v>0.8194784018954933</v>
       </c>
       <c r="D50">
-        <v>-1.212473893379038</v>
+        <v>-1.212473893379076</v>
       </c>
       <c r="E50">
-        <v>0.2253310301018446</v>
+        <v>0.2253310301018299</v>
       </c>
       <c r="F50">
-        <v>0.1602211589914752</v>
+        <v>0.07429257073912629</v>
       </c>
       <c r="G50">
-        <v>1.539515175550091</v>
+        <v>1.84513415085055</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3521,26 +3521,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B51">
-        <v>0.8161427420880236</v>
+        <v>0.6811024871515554</v>
       </c>
       <c r="C51">
-        <v>0.5593216616624586</v>
+        <v>0.7855938217430087</v>
       </c>
       <c r="D51">
-        <v>-0.3632364419483101</v>
+        <v>-0.4888563000925151</v>
       </c>
       <c r="E51">
-        <v>0.7164282672590141</v>
+        <v>0.6249434358254521</v>
       </c>
       <c r="F51">
-        <v>0.2726909100275667</v>
+        <v>0.1460541134075082</v>
       </c>
       <c r="G51">
-        <v>2.442651921898028</v>
+        <v>3.176224121190597</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3584,26 +3584,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B52">
-        <v>0.790008790046843</v>
+        <v>1.556898112675424</v>
       </c>
       <c r="C52">
-        <v>0.5722908393927975</v>
+        <v>0.8164631048440749</v>
       </c>
       <c r="D52">
-        <v>-0.4118731084206895</v>
+        <v>0.5422112154901745</v>
       </c>
       <c r="E52">
-        <v>0.6804324321868978</v>
+        <v>0.5876730099270254</v>
       </c>
       <c r="F52">
-        <v>0.2573339449618668</v>
+        <v>0.314257417579187</v>
       </c>
       <c r="G52">
-        <v>2.425307273176734</v>
+        <v>7.713204518526635</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3647,26 +3647,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B53">
-        <v>2.250408146201904</v>
+        <v>1.797232689208659</v>
       </c>
       <c r="C53">
-        <v>0.5080320929111251</v>
+        <v>0.6877380631569141</v>
       </c>
       <c r="D53">
-        <v>1.596575510475669</v>
+        <v>0.8524293163633084</v>
       </c>
       <c r="E53">
-        <v>0.1103603614399558</v>
+        <v>0.3939758546142765</v>
       </c>
       <c r="F53">
-        <v>0.8314259776192972</v>
+        <v>0.4668749885727888</v>
       </c>
       <c r="G53">
-        <v>6.091145767411668</v>
+        <v>6.918437308098812</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3704,32 +3704,32 @@
         </is>
       </c>
       <c r="O53">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B54">
-        <v>0.7320817304436906</v>
+        <v>0.6466207434362474</v>
       </c>
       <c r="C54">
-        <v>0.3297042424024026</v>
+        <v>0.460937837673433</v>
       </c>
       <c r="D54">
-        <v>-0.9458874880396572</v>
+        <v>-0.9458874880396489</v>
       </c>
       <c r="E54">
-        <v>0.3442059758438713</v>
+        <v>0.3442059758438755</v>
       </c>
       <c r="F54">
-        <v>0.3836319850083993</v>
+        <v>0.2619983967876028</v>
       </c>
       <c r="G54">
-        <v>1.397025485342924</v>
+        <v>1.595881467095412</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3773,26 +3773,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.528022103576878</v>
+        <v>6.233435131953863</v>
       </c>
       <c r="C55">
-        <v>0.4633651355341439</v>
+        <v>1.999944152621403</v>
       </c>
       <c r="D55">
-        <v>0.9149893330723723</v>
+        <v>0.9149893330721347</v>
       </c>
       <c r="E55">
-        <v>0.3601972300290032</v>
+        <v>0.360197230029128</v>
       </c>
       <c r="F55">
-        <v>0.6161869809483991</v>
+        <v>0.1237006253969706</v>
       </c>
       <c r="G55">
-        <v>3.789193250116774</v>
+        <v>314.1108900588329</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9781171056046367</v>
+        <v>0.9412035662656106</v>
       </c>
       <c r="C57">
-        <v>0.393049893274935</v>
+        <v>0.3892785049139516</v>
       </c>
       <c r="D57">
-        <v>-0.0562927928797291</v>
+        <v>-0.1556619035181968</v>
       </c>
       <c r="E57">
-        <v>0.9551085601812525</v>
+        <v>0.8762995276334116</v>
       </c>
       <c r="F57">
-        <v>0.4527163488135083</v>
+        <v>0.4388631337848676</v>
       </c>
       <c r="G57">
-        <v>2.113272637013822</v>
+        <v>2.018543105936434</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.9610743843054839</v>
+        <v>1.219896775952729</v>
       </c>
       <c r="C58">
-        <v>0.3904059311525785</v>
+        <v>0.3672241936583561</v>
       </c>
       <c r="D58">
-        <v>-0.101697917003189</v>
+        <v>0.5412667485510397</v>
       </c>
       <c r="E58">
-        <v>0.9189964555657603</v>
+        <v>0.5883237359783478</v>
       </c>
       <c r="F58">
-        <v>0.4471393292485787</v>
+        <v>0.59393823379788</v>
       </c>
       <c r="G58">
-        <v>2.06571847240633</v>
+        <v>2.505560442647454</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.464450041354151</v>
+        <v>1.296066809706831</v>
       </c>
       <c r="C59">
-        <v>0.3018479018694842</v>
+        <v>0.3001202477614935</v>
       </c>
       <c r="D59">
-        <v>1.26381456102117</v>
+        <v>0.8641008037125174</v>
       </c>
       <c r="E59">
-        <v>0.2062965936024148</v>
+        <v>0.3875325175435274</v>
       </c>
       <c r="F59">
-        <v>0.8104778695425632</v>
+        <v>0.7197216569090195</v>
       </c>
       <c r="G59">
-        <v>2.646110405004151</v>
+        <v>2.333942794548956</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="60">
@@ -4214,26 +4214,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B62">
-        <v>0.7838822476555993</v>
+        <v>0.7086363709773947</v>
       </c>
       <c r="C62">
-        <v>0.5379549160244986</v>
+        <v>0.7609085328293408</v>
       </c>
       <c r="D62">
-        <v>-0.4526335887555563</v>
+        <v>-0.4526335887555357</v>
       </c>
       <c r="E62">
-        <v>0.6508126080584504</v>
+        <v>0.6508126080584653</v>
       </c>
       <c r="F62">
-        <v>0.2731132526517962</v>
+        <v>0.1594912719128614</v>
       </c>
       <c r="G62">
-        <v>2.249877558937098</v>
+        <v>3.14854537335668</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4277,26 +4277,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B63">
-        <v>0.9986692762052947</v>
+        <v>0.9191457622460868</v>
       </c>
       <c r="C63">
-        <v>0.532221608664335</v>
+        <v>0.7427159645336119</v>
       </c>
       <c r="D63">
-        <v>-0.002501984083724433</v>
+        <v>-0.1135165576127006</v>
       </c>
       <c r="E63">
-        <v>0.9980037076109952</v>
+        <v>0.9096210368516534</v>
       </c>
       <c r="F63">
-        <v>0.3518793932987754</v>
+        <v>0.21437957915363</v>
       </c>
       <c r="G63">
-        <v>2.83432432313415</v>
+        <v>3.940808800867705</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,26 +4340,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B64">
-        <v>1.007091820263621</v>
+        <v>1.974228046675315</v>
       </c>
       <c r="C64">
-        <v>0.5401641422362209</v>
+        <v>0.7382907525973189</v>
       </c>
       <c r="D64">
-        <v>0.01308267435161139</v>
+        <v>0.9212867113812495</v>
       </c>
       <c r="E64">
-        <v>0.9895618338814542</v>
+        <v>0.3569007571270047</v>
       </c>
       <c r="F64">
-        <v>0.349365903133794</v>
+        <v>0.4644757978682965</v>
       </c>
       <c r="G64">
-        <v>2.903070750019589</v>
+        <v>8.391344389023685</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4403,26 +4403,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B65">
-        <v>2.129921523086084</v>
+        <v>1.784854895511504</v>
       </c>
       <c r="C65">
-        <v>0.4777120769161904</v>
+        <v>0.6518825364142082</v>
       </c>
       <c r="D65">
-        <v>1.582721417264235</v>
+        <v>0.8887139761161287</v>
       </c>
       <c r="E65">
-        <v>0.1134849745392866</v>
+        <v>0.3741568179174121</v>
       </c>
       <c r="F65">
-        <v>0.835092041959505</v>
+        <v>0.4974157056468348</v>
       </c>
       <c r="G65">
-        <v>5.432413993385091</v>
+        <v>6.404516306715164</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4460,32 +4460,32 @@
         </is>
       </c>
       <c r="O65">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B66">
-        <v>0.7904591169363303</v>
+        <v>0.7339600521665998</v>
       </c>
       <c r="C66">
-        <v>0.3620364142816582</v>
+        <v>0.4762161648718247</v>
       </c>
       <c r="D66">
-        <v>-0.6494963831668656</v>
+        <v>-0.6494963831668776</v>
       </c>
       <c r="E66">
-        <v>0.5160175834827607</v>
+        <v>0.5160175834827531</v>
       </c>
       <c r="F66">
-        <v>0.3887885428786643</v>
+        <v>0.2886133982623763</v>
       </c>
       <c r="G66">
-        <v>1.607109126522699</v>
+        <v>1.86650156028679</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4529,26 +4529,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B67">
-        <v>1.5436997884702</v>
+        <v>6.60004893168239</v>
       </c>
       <c r="C67">
-        <v>0.3247894505457771</v>
+        <v>1.411626297733609</v>
       </c>
       <c r="D67">
-        <v>1.336810645937724</v>
+        <v>1.336810645937883</v>
       </c>
       <c r="E67">
-        <v>0.181284453275584</v>
+        <v>0.1812844532755323</v>
       </c>
       <c r="F67">
-        <v>0.8167733577917711</v>
+        <v>0.4149241111005003</v>
       </c>
       <c r="G67">
-        <v>2.917589089053596</v>
+        <v>104.9846098002506</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4592,26 +4592,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B68">
-        <v>0.861641304937977</v>
+        <v>0.8543697167868356</v>
       </c>
       <c r="C68">
-        <v>0.4205932786748806</v>
+        <v>0.4445298606772241</v>
       </c>
       <c r="D68">
-        <v>-0.3540622782915134</v>
+        <v>-0.3540622782915127</v>
       </c>
       <c r="E68">
-        <v>0.7232922108565993</v>
+        <v>0.7232922108565999</v>
       </c>
       <c r="F68">
-        <v>0.3778477686856954</v>
+        <v>0.3574878969094318</v>
       </c>
       <c r="G68">
-        <v>1.964880568059648</v>
+        <v>2.041880632247942</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4655,26 +4655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B69">
-        <v>0.9766451588436276</v>
+        <v>0.9184127359829509</v>
       </c>
       <c r="C69">
-        <v>0.4387347755859351</v>
+        <v>0.4595056404748462</v>
       </c>
       <c r="D69">
-        <v>-0.05386372099605802</v>
+        <v>-0.1852172823118871</v>
       </c>
       <c r="E69">
-        <v>0.9570437411356159</v>
+        <v>0.8530586142870896</v>
       </c>
       <c r="F69">
-        <v>0.4133187274636047</v>
+        <v>0.3731693682732486</v>
       </c>
       <c r="G69">
-        <v>2.307748724927267</v>
+        <v>2.260319375941009</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4718,26 +4718,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B70">
-        <v>0.8244166969177752</v>
+        <v>1.199756557213543</v>
       </c>
       <c r="C70">
-        <v>0.4429614745446395</v>
+        <v>0.4347875290049268</v>
       </c>
       <c r="D70">
-        <v>-0.4358825492701</v>
+        <v>0.4188681944060081</v>
       </c>
       <c r="E70">
-        <v>0.6629219469311791</v>
+        <v>0.6753124627395101</v>
       </c>
       <c r="F70">
-        <v>0.3460168819335563</v>
+        <v>0.5116833867107436</v>
       </c>
       <c r="G70">
-        <v>1.964247774151454</v>
+        <v>2.8130985565701</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4781,26 +4781,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B71">
-        <v>1.695921897630296</v>
+        <v>1.452015255130247</v>
       </c>
       <c r="C71">
-        <v>0.3327291304257664</v>
+        <v>0.3642482710975187</v>
       </c>
       <c r="D71">
-        <v>1.587557075955067</v>
+        <v>1.023896205496644</v>
       </c>
       <c r="E71">
-        <v>0.1123865309499154</v>
+        <v>0.3058843026749437</v>
       </c>
       <c r="F71">
-        <v>0.8834587948428125</v>
+        <v>0.711086590164249</v>
       </c>
       <c r="G71">
-        <v>3.255557700768237</v>
+        <v>2.964967038183019</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4838,32 +4838,32 @@
         </is>
       </c>
       <c r="O71">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B72">
-        <v>0.744516081889312</v>
+        <v>0.7399712540963133</v>
       </c>
       <c r="C72">
-        <v>0.2975203117691659</v>
+        <v>0.3036953014083394</v>
       </c>
       <c r="D72">
-        <v>-0.9915989412998214</v>
+        <v>-0.9915989412997993</v>
       </c>
       <c r="E72">
-        <v>0.321393205940837</v>
+        <v>0.321393205940848</v>
       </c>
       <c r="F72">
-        <v>0.4155510027569823</v>
+        <v>0.4080458259466174</v>
       </c>
       <c r="G72">
-        <v>1.333901717272415</v>
+        <v>1.341901870013259</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4907,26 +4907,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B73">
-        <v>1.223630409466774</v>
+        <v>1.759261133756516</v>
       </c>
       <c r="C73">
-        <v>0.2378868840539315</v>
+        <v>0.6658378607099783</v>
       </c>
       <c r="D73">
-        <v>0.8483955987979424</v>
+        <v>0.8483955987979719</v>
       </c>
       <c r="E73">
-        <v>0.3962176929373393</v>
+        <v>0.3962176929373228</v>
       </c>
       <c r="F73">
-        <v>0.7676452706612332</v>
+        <v>0.4770546063163482</v>
       </c>
       <c r="G73">
-        <v>1.95047300647356</v>
+        <v>6.487726343625077</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>1.323360397619435</v>
+        <v>1.477119534737568</v>
       </c>
       <c r="C74">
-        <v>0.4675328567495403</v>
+        <v>0.4850427777990784</v>
       </c>
       <c r="D74">
-        <v>0.5992611072755841</v>
+        <v>0.8042464477216342</v>
       </c>
       <c r="E74">
-        <v>0.5489987790976769</v>
+        <v>0.4212546587937106</v>
       </c>
       <c r="F74">
-        <v>0.5293140778329168</v>
+        <v>0.5708821719861868</v>
       </c>
       <c r="G74">
-        <v>3.308589012326023</v>
+        <v>3.821948253020803</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.393076639806953</v>
+        <v>1.049587409748841</v>
       </c>
       <c r="C75">
-        <v>0.4728277936408928</v>
+        <v>0.4663896639649615</v>
       </c>
       <c r="D75">
-        <v>0.7011320306274547</v>
+        <v>0.1037697607603025</v>
       </c>
       <c r="E75">
-        <v>0.4832206225967849</v>
+        <v>0.9173520643003368</v>
       </c>
       <c r="F75">
-        <v>0.5514463443931753</v>
+        <v>0.4207527961576428</v>
       </c>
       <c r="G75">
-        <v>3.519222756860203</v>
+        <v>2.618244586283236</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.8970395975518303</v>
+        <v>1.38121010207883</v>
       </c>
       <c r="C76">
-        <v>0.4730078878346008</v>
+        <v>0.4529107512633434</v>
       </c>
       <c r="D76">
-        <v>-0.2297113351897573</v>
+        <v>0.7130764716736848</v>
       </c>
       <c r="E76">
-        <v>0.8183160862200112</v>
+        <v>0.4757984378821244</v>
       </c>
       <c r="F76">
-        <v>0.3549658476175095</v>
+        <v>0.5685143295632581</v>
       </c>
       <c r="G76">
-        <v>2.266922423598976</v>
+        <v>3.355660969091439</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>2.402787129094381</v>
+        <v>1.77125169939446</v>
       </c>
       <c r="C77">
-        <v>0.4177366331818738</v>
+        <v>0.4219986608829095</v>
       </c>
       <c r="D77">
-        <v>2.098521646699619</v>
+        <v>1.354711577184876</v>
       </c>
       <c r="E77">
-        <v>0.03585908974332108</v>
+        <v>0.1755094678764351</v>
       </c>
       <c r="F77">
-        <v>1.059588485258305</v>
+        <v>0.7745944279360591</v>
       </c>
       <c r="G77">
-        <v>5.448705858986555</v>
+        <v>4.050290667552724</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
         </is>
       </c>
       <c r="O77">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B78">
-        <v>1.432967985740417</v>
+        <v>2.079998502917444</v>
       </c>
       <c r="C78">
-        <v>0.5874381541900311</v>
+        <v>0.8425138123592476</v>
       </c>
       <c r="D78">
-        <v>0.6124011613904173</v>
+        <v>0.8692642936154708</v>
       </c>
       <c r="E78">
-        <v>0.5402723736027131</v>
+        <v>0.3847025882139093</v>
       </c>
       <c r="F78">
-        <v>0.4531147757516789</v>
+        <v>0.3989458623067144</v>
       </c>
       <c r="G78">
-        <v>4.531737559761845</v>
+        <v>10.84456358846159</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5279,32 +5279,32 @@
         </is>
       </c>
       <c r="O78">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.216235026618361</v>
+        <v>0.8336401052834277</v>
       </c>
       <c r="C79">
-        <v>0.5483830919047015</v>
+        <v>0.8250588941139501</v>
       </c>
       <c r="D79">
-        <v>0.3569768036742543</v>
+        <v>-0.2205339515685388</v>
       </c>
       <c r="E79">
-        <v>0.7211091711776684</v>
+        <v>0.8254553336512732</v>
       </c>
       <c r="F79">
-        <v>0.4151766998804444</v>
+        <v>0.1654577811030573</v>
       </c>
       <c r="G79">
-        <v>3.562886935609172</v>
+        <v>4.20020032000854</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5342,32 +5342,32 @@
         </is>
       </c>
       <c r="O79">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B80">
-        <v>0.9767163970504608</v>
+        <v>1.809282341398598</v>
       </c>
       <c r="C80">
-        <v>0.5607139368514684</v>
+        <v>0.8531916245386251</v>
       </c>
       <c r="D80">
-        <v>-0.04201598516709587</v>
+        <v>0.6949555681679357</v>
       </c>
       <c r="E80">
-        <v>0.9664859550490705</v>
+        <v>0.487083146958454</v>
       </c>
       <c r="F80">
-        <v>0.3254527235890146</v>
+        <v>0.339835165657137</v>
       </c>
       <c r="G80">
-        <v>2.931224264301821</v>
+        <v>9.632618756704716</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5405,32 +5405,32 @@
         </is>
       </c>
       <c r="O80">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B81">
-        <v>2.15977065180271</v>
+        <v>1.829247013330386</v>
       </c>
       <c r="C81">
-        <v>0.5378579240220842</v>
+        <v>0.7799402396311605</v>
       </c>
       <c r="D81">
-        <v>1.431608612511627</v>
+        <v>0.7742957516042646</v>
       </c>
       <c r="E81">
-        <v>0.1522558634466848</v>
+        <v>0.4387559154396171</v>
       </c>
       <c r="F81">
-        <v>0.7526310659203321</v>
+        <v>0.3966304192670967</v>
       </c>
       <c r="G81">
-        <v>6.197736819014141</v>
+        <v>8.436429666592955</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5468,32 +5468,32 @@
         </is>
       </c>
       <c r="O81">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B82">
-        <v>1.239790251520656</v>
+        <v>1.594567191655911</v>
       </c>
       <c r="C82">
-        <v>0.4925142785506292</v>
+        <v>0.6978060892199746</v>
       </c>
       <c r="D82">
-        <v>0.4364182373396219</v>
+        <v>0.6686704994816859</v>
       </c>
       <c r="E82">
-        <v>0.6625333094101316</v>
+        <v>0.5037056899062842</v>
       </c>
       <c r="F82">
-        <v>0.4721927375298596</v>
+        <v>0.4061338650537912</v>
       </c>
       <c r="G82">
-        <v>3.25519590963309</v>
+        <v>6.260607025145892</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5531,32 +5531,32 @@
         </is>
       </c>
       <c r="O82">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.264904996504551</v>
+        <v>0.8805893742456238</v>
       </c>
       <c r="C83">
-        <v>0.4691298308420679</v>
+        <v>0.6903151442964844</v>
       </c>
       <c r="D83">
-        <v>0.5009210720196139</v>
+        <v>-0.184211303022487</v>
       </c>
       <c r="E83">
-        <v>0.6164266718190802</v>
+        <v>0.8538476926893339</v>
       </c>
       <c r="F83">
-        <v>0.504352144873607</v>
+        <v>0.2276020264909755</v>
       </c>
       <c r="G83">
-        <v>3.172356192880159</v>
+        <v>3.406989199479055</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5594,32 +5594,32 @@
         </is>
       </c>
       <c r="O83">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B84">
-        <v>0.8607029424931689</v>
+        <v>1.45164608779106</v>
       </c>
       <c r="C84">
-        <v>0.4798124037153662</v>
+        <v>0.7007610768273423</v>
       </c>
       <c r="D84">
-        <v>-0.3126343701204805</v>
+        <v>0.5318476693790317</v>
       </c>
       <c r="E84">
-        <v>0.7545584625609837</v>
+        <v>0.5948315038924467</v>
       </c>
       <c r="F84">
-        <v>0.3360750169424027</v>
+        <v>0.3675968980769771</v>
       </c>
       <c r="G84">
-        <v>2.204298200908402</v>
+        <v>5.732573847121563</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5657,32 +5657,32 @@
         </is>
       </c>
       <c r="O84">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B85">
-        <v>2.151194660370783</v>
+        <v>1.88898981609645</v>
       </c>
       <c r="C85">
-        <v>0.4439446840213705</v>
+        <v>0.6433362832645755</v>
       </c>
       <c r="D85">
-        <v>1.725492772810144</v>
+        <v>0.9886620945985748</v>
       </c>
       <c r="E85">
-        <v>0.08443870512554061</v>
+        <v>0.3228284944406485</v>
       </c>
       <c r="F85">
-        <v>0.9011421650212336</v>
+        <v>0.5353290107165233</v>
       </c>
       <c r="G85">
-        <v>5.135303447596117</v>
+        <v>6.665587804666239</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>1.018563089752933</v>
+        <v>1.228906456813475</v>
       </c>
       <c r="C86">
-        <v>0.3403178199987566</v>
+        <v>0.3747201168015372</v>
       </c>
       <c r="D86">
-        <v>0.05404623995041009</v>
+        <v>0.5500764575830227</v>
       </c>
       <c r="E86">
-        <v>0.9568983238991683</v>
+        <v>0.5822669333628163</v>
       </c>
       <c r="F86">
-        <v>0.522767862012792</v>
+        <v>0.5895986553177003</v>
       </c>
       <c r="G86">
-        <v>1.984572586027975</v>
+        <v>2.561422191141336</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.129438080531383</v>
+        <v>0.8203529451666439</v>
       </c>
       <c r="C87">
-        <v>0.3939472621567091</v>
+        <v>0.3861965301862532</v>
       </c>
       <c r="D87">
-        <v>0.3089759642196575</v>
+        <v>-0.5127457004803359</v>
       </c>
       <c r="E87">
-        <v>0.757339810621165</v>
+        <v>0.6081292172331382</v>
       </c>
       <c r="F87">
-        <v>0.5218358467105201</v>
+        <v>0.3848306542649435</v>
       </c>
       <c r="G87">
-        <v>2.444505079127019</v>
+        <v>1.74876649556161</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.7360872970186105</v>
+        <v>1.119369604199397</v>
       </c>
       <c r="C88">
-        <v>0.3961354262089898</v>
+        <v>0.3600417432145793</v>
       </c>
       <c r="D88">
-        <v>-0.773489410274543</v>
+        <v>0.3132016650218443</v>
       </c>
       <c r="E88">
-        <v>0.439232793544037</v>
+        <v>0.7541274535189231</v>
       </c>
       <c r="F88">
-        <v>0.3386399855035597</v>
+        <v>0.5527203087617363</v>
       </c>
       <c r="G88">
-        <v>1.600001571068071</v>
+        <v>2.266948203174577</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.731826787450101</v>
+        <v>1.312861906369791</v>
       </c>
       <c r="C89">
-        <v>0.2962255988034107</v>
+        <v>0.32998636240776</v>
       </c>
       <c r="D89">
-        <v>1.853914044267813</v>
+        <v>0.8249111074626665</v>
       </c>
       <c r="E89">
-        <v>0.06375145831472484</v>
+        <v>0.4094220597814392</v>
       </c>
       <c r="F89">
-        <v>0.9690736080657945</v>
+        <v>0.6875972739644682</v>
       </c>
       <c r="G89">
-        <v>3.094939328412821</v>
+        <v>2.506709160231472</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,32 +5972,32 @@
         </is>
       </c>
       <c r="O89">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B90">
-        <v>1.459697768867063</v>
+        <v>2.272173405418178</v>
       </c>
       <c r="C90">
-        <v>0.457088216590658</v>
+        <v>0.677618445128704</v>
       </c>
       <c r="D90">
-        <v>0.8274757321180962</v>
+        <v>1.211207910076705</v>
       </c>
       <c r="E90">
-        <v>0.4079674714721176</v>
+        <v>0.2258157319260407</v>
       </c>
       <c r="F90">
-        <v>0.5959210807046965</v>
+        <v>0.6020764026902083</v>
       </c>
       <c r="G90">
-        <v>3.575502940617298</v>
+        <v>8.574944909352451</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6035,32 +6035,32 @@
         </is>
       </c>
       <c r="O90">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B91">
-        <v>1.169771264066933</v>
+        <v>0.7820429243331545</v>
       </c>
       <c r="C91">
-        <v>0.4672318854873453</v>
+        <v>0.6835586522040138</v>
       </c>
       <c r="D91">
-        <v>0.3356111467774539</v>
+        <v>-0.3596555302152373</v>
       </c>
       <c r="E91">
-        <v>0.7371641171809507</v>
+        <v>0.7191047513435769</v>
       </c>
       <c r="F91">
-        <v>0.4681579972466267</v>
+        <v>0.2048256828512302</v>
       </c>
       <c r="G91">
-        <v>2.922869668540328</v>
+        <v>2.985910394565927</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6098,32 +6098,32 @@
         </is>
       </c>
       <c r="O91">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B92">
-        <v>1.005406764404261</v>
+        <v>1.950819217118842</v>
       </c>
       <c r="C92">
-        <v>0.4655500550617794</v>
+        <v>0.6521565751802264</v>
       </c>
       <c r="D92">
-        <v>0.01158242871576358</v>
+        <v>1.024676314138081</v>
       </c>
       <c r="E92">
-        <v>0.9907587655742434</v>
+        <v>0.3055159426931401</v>
       </c>
       <c r="F92">
-        <v>0.4037056964602985</v>
+        <v>0.5433758616497314</v>
       </c>
       <c r="G92">
-        <v>2.503910077992308</v>
+        <v>7.00379955474243</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6161,32 +6161,32 @@
         </is>
       </c>
       <c r="O92">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B93">
-        <v>2.032262134126402</v>
+        <v>1.630391242325126</v>
       </c>
       <c r="C93">
-        <v>0.4086463046889652</v>
+        <v>0.6309330414576048</v>
       </c>
       <c r="D93">
-        <v>1.735362626001921</v>
+        <v>0.7747573511986193</v>
       </c>
       <c r="E93">
-        <v>0.08267659555654509</v>
+        <v>0.438483054908176</v>
       </c>
       <c r="F93">
-        <v>0.9123035401286125</v>
+        <v>0.4734135185903582</v>
       </c>
       <c r="G93">
-        <v>4.527100027718578</v>
+        <v>5.614912753158136</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6224,32 +6224,32 @@
         </is>
       </c>
       <c r="O93">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B94">
-        <v>1.025912482769998</v>
+        <v>1.241277386115368</v>
       </c>
       <c r="C94">
-        <v>0.3496568190910352</v>
+        <v>0.3975780828564991</v>
       </c>
       <c r="D94">
-        <v>0.07316443515224794</v>
+        <v>0.5436441513993394</v>
       </c>
       <c r="E94">
-        <v>0.9416752671466871</v>
+        <v>0.5866863710883716</v>
       </c>
       <c r="F94">
-        <v>0.5169896992769322</v>
+        <v>0.5694423536419085</v>
       </c>
       <c r="G94">
-        <v>2.035817007138316</v>
+        <v>2.705751582100104</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6287,32 +6287,32 @@
         </is>
       </c>
       <c r="O94">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.176778158563494</v>
+        <v>0.8385553751736146</v>
       </c>
       <c r="C95">
-        <v>0.3817917940992119</v>
+        <v>0.4047462032976045</v>
       </c>
       <c r="D95">
-        <v>0.4263589019577715</v>
+        <v>-0.4350248568344209</v>
       </c>
       <c r="E95">
-        <v>0.6698463436167376</v>
+        <v>0.6635443850571786</v>
       </c>
       <c r="F95">
-        <v>0.5568174470685779</v>
+        <v>0.3793247272974323</v>
       </c>
       <c r="G95">
-        <v>2.48700331098198</v>
+        <v>1.853755019459079</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6350,32 +6350,32 @@
         </is>
       </c>
       <c r="O95">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B96">
-        <v>0.7190794960583242</v>
+        <v>1.116129759156283</v>
       </c>
       <c r="C96">
-        <v>0.387065912979121</v>
+        <v>0.3775095434408557</v>
       </c>
       <c r="D96">
-        <v>-0.8520082796245498</v>
+        <v>0.291031394449299</v>
       </c>
       <c r="E96">
-        <v>0.3942094966777167</v>
+        <v>0.7710273089241113</v>
       </c>
       <c r="F96">
-        <v>0.3367486031608075</v>
+        <v>0.5325715734911869</v>
       </c>
       <c r="G96">
-        <v>1.535493590168137</v>
+        <v>2.339114029515279</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6413,32 +6413,32 @@
         </is>
       </c>
       <c r="O96">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B97">
-        <v>1.842942502395029</v>
+        <v>1.424277064909621</v>
       </c>
       <c r="C97">
-        <v>0.2950340459960498</v>
+        <v>0.3566240908811683</v>
       </c>
       <c r="D97">
-        <v>2.072179426969885</v>
+        <v>0.9917007043593963</v>
       </c>
       <c r="E97">
-        <v>0.03824871127033096</v>
+        <v>0.3213435473637036</v>
       </c>
       <c r="F97">
-        <v>1.033661523725856</v>
+        <v>0.7080036626778178</v>
       </c>
       <c r="G97">
-        <v>3.285830989327645</v>
+        <v>2.865190202484415</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.6377855970610409</v>
+        <v>0.6885983521972606</v>
       </c>
       <c r="C98">
-        <v>0.9746534130552451</v>
+        <v>0.9687603370553316</v>
       </c>
       <c r="D98">
-        <v>-0.4614492709462957</v>
+        <v>-0.3851284025416198</v>
       </c>
       <c r="E98">
-        <v>0.6444763089960139</v>
+        <v>0.7001422857935276</v>
       </c>
       <c r="F98">
-        <v>0.09441656978248417</v>
+        <v>0.1031230347647921</v>
       </c>
       <c r="G98">
-        <v>4.308252976735139</v>
+        <v>4.59807735226457</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.649033645255008</v>
+        <v>1.371966641789392</v>
       </c>
       <c r="C99">
-        <v>0.7683250767801978</v>
+        <v>0.8480437742403383</v>
       </c>
       <c r="D99">
-        <v>0.6510127834103802</v>
+        <v>0.3729114286898901</v>
       </c>
       <c r="E99">
-        <v>0.5150382349141378</v>
+        <v>0.7092143657247119</v>
       </c>
       <c r="F99">
-        <v>0.365788481474385</v>
+        <v>0.2603079204249534</v>
       </c>
       <c r="G99">
-        <v>7.43411042420548</v>
+        <v>7.231022640840182</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.7179119848511224</v>
+        <v>1.328713817059287</v>
       </c>
       <c r="C100">
-        <v>0.8731847235840832</v>
+        <v>0.9737026574547877</v>
       </c>
       <c r="D100">
-        <v>-0.3795397380068969</v>
+        <v>0.2918872792590724</v>
       </c>
       <c r="E100">
-        <v>0.7042871010676217</v>
+        <v>0.7703728098661844</v>
       </c>
       <c r="F100">
-        <v>0.1296626876124503</v>
+        <v>0.1970671548498312</v>
       </c>
       <c r="G100">
-        <v>3.974910804975398</v>
+        <v>8.95877554526826</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>2.505473299182749</v>
+        <v>2.099966846816803</v>
       </c>
       <c r="C101">
-        <v>0.8321397229457683</v>
+        <v>0.7987429126140027</v>
       </c>
       <c r="D101">
-        <v>1.103754133053152</v>
+        <v>0.9288615218463939</v>
       </c>
       <c r="E101">
-        <v>0.2696998062950445</v>
+        <v>0.3529608562223822</v>
       </c>
       <c r="F101">
-        <v>0.4904233758460037</v>
+        <v>0.4388551897341307</v>
       </c>
       <c r="G101">
-        <v>12.79995359537845</v>
+        <v>10.04855556203245</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
         </is>
       </c>
       <c r="O101">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B102">
-        <v>0.3441567840411972</v>
+        <v>0.2324410972872197</v>
       </c>
       <c r="C102">
-        <v>1.061304319484024</v>
+        <v>1.527925638533233</v>
       </c>
       <c r="D102">
-        <v>-1.005044395179872</v>
+        <v>-0.9549669134774857</v>
       </c>
       <c r="E102">
-        <v>0.3148754730923183</v>
+        <v>0.3395944292102273</v>
       </c>
       <c r="F102">
-        <v>0.04299049644153573</v>
+        <v>0.01163429992675574</v>
       </c>
       <c r="G102">
-        <v>2.755118033183337</v>
+        <v>4.643929075941645</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6791,32 +6791,32 @@
         </is>
       </c>
       <c r="O102">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B103">
-        <v>1.439191898485976</v>
+        <v>0.7799548094234894</v>
       </c>
       <c r="C103">
-        <v>0.8624294108323385</v>
+        <v>1.404817856995181</v>
       </c>
       <c r="D103">
-        <v>0.4221583469750145</v>
+        <v>-0.1769049961715399</v>
       </c>
       <c r="E103">
-        <v>0.6729094421909825</v>
+        <v>0.8595830141433052</v>
       </c>
       <c r="F103">
-        <v>0.2654712288780494</v>
+        <v>0.04969198123968186</v>
       </c>
       <c r="G103">
-        <v>7.802251601506534</v>
+        <v>12.24200544165556</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6854,32 +6854,32 @@
         </is>
       </c>
       <c r="O103">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B104">
-        <v>0.3922574562670297</v>
+        <v>0.5879288636977622</v>
       </c>
       <c r="C104">
-        <v>0.9241372067021396</v>
+        <v>1.552923542547135</v>
       </c>
       <c r="D104">
-        <v>-1.012660102630191</v>
+        <v>-0.3420318540839677</v>
       </c>
       <c r="E104">
-        <v>0.3112225410495655</v>
+        <v>0.7323269202510989</v>
       </c>
       <c r="F104">
-        <v>0.06411271835304092</v>
+        <v>0.02802037001854964</v>
       </c>
       <c r="G104">
-        <v>2.399928063411817</v>
+        <v>12.33603798023055</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6917,32 +6917,32 @@
         </is>
       </c>
       <c r="O104">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B105">
-        <v>1.862390668682007</v>
+        <v>1.341175466487839</v>
       </c>
       <c r="C105">
-        <v>0.951359350623587</v>
+        <v>1.356256716804162</v>
       </c>
       <c r="D105">
-        <v>0.6536551806235839</v>
+        <v>0.2164387019031717</v>
       </c>
       <c r="E105">
-        <v>0.5133339847822815</v>
+        <v>0.828645801376011</v>
       </c>
       <c r="F105">
-        <v>0.288583993889758</v>
+        <v>0.09398050841563117</v>
       </c>
       <c r="G105">
-        <v>12.01902765306802</v>
+        <v>19.13962439907057</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6980,32 +6980,32 @@
         </is>
       </c>
       <c r="O105">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B106">
-        <v>0.3836281048430353</v>
+        <v>0.2660315231981485</v>
       </c>
       <c r="C106">
-        <v>0.9443951854264896</v>
+        <v>1.330852232917719</v>
       </c>
       <c r="D106">
-        <v>-1.014492330570107</v>
+        <v>-0.9949567925022502</v>
       </c>
       <c r="E106">
-        <v>0.31034788717463</v>
+        <v>0.3197572792504023</v>
       </c>
       <c r="F106">
-        <v>0.06026147771555735</v>
+        <v>0.01959339196525166</v>
       </c>
       <c r="G106">
-        <v>2.442199036673552</v>
+        <v>3.612073471537781</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7043,32 +7043,32 @@
         </is>
       </c>
       <c r="O106">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B107">
-        <v>1.450659026772991</v>
+        <v>0.9632619053030549</v>
       </c>
       <c r="C107">
-        <v>0.753884548166207</v>
+        <v>1.218028905387669</v>
       </c>
       <c r="D107">
-        <v>0.4934680718762017</v>
+        <v>-0.03072992428295063</v>
       </c>
       <c r="E107">
-        <v>0.6216818942924103</v>
+        <v>0.9754849263001303</v>
       </c>
       <c r="F107">
-        <v>0.331022606449681</v>
+        <v>0.08850265541531294</v>
       </c>
       <c r="G107">
-        <v>6.357304821348674</v>
+        <v>10.48413173428386</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7106,32 +7106,32 @@
         </is>
       </c>
       <c r="O107">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B108">
-        <v>0.4422799486658444</v>
+        <v>0.6562671144749616</v>
       </c>
       <c r="C108">
-        <v>0.8361719995461793</v>
+        <v>1.365136278929926</v>
       </c>
       <c r="D108">
-        <v>-0.9756512174741686</v>
+        <v>-0.3085313845344216</v>
       </c>
       <c r="E108">
-        <v>0.3292373342582672</v>
+        <v>0.7576780228290454</v>
       </c>
       <c r="F108">
-        <v>0.08589074190707661</v>
+        <v>0.04519334999789579</v>
       </c>
       <c r="G108">
-        <v>2.277446307350447</v>
+        <v>9.529865025747041</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7169,32 +7169,32 @@
         </is>
       </c>
       <c r="O108">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B109">
-        <v>1.873304205424117</v>
+        <v>1.650176134890761</v>
       </c>
       <c r="C109">
-        <v>0.8030112512461144</v>
+        <v>1.156129037322684</v>
       </c>
       <c r="D109">
-        <v>0.7816874613357513</v>
+        <v>0.4332405937955225</v>
       </c>
       <c r="E109">
-        <v>0.4343982723104205</v>
+        <v>0.6648399908697898</v>
       </c>
       <c r="F109">
-        <v>0.3882253514659493</v>
+        <v>0.1711715097731414</v>
       </c>
       <c r="G109">
-        <v>9.039256794561689</v>
+        <v>15.90849598611352</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.6760578875831099</v>
+        <v>0.7777531249426309</v>
       </c>
       <c r="C110">
-        <v>0.4678411202514733</v>
+        <v>0.5346127238295441</v>
       </c>
       <c r="D110">
-        <v>-0.8367724792459638</v>
+        <v>-0.4701461713913898</v>
       </c>
       <c r="E110">
-        <v>0.4027204695875595</v>
+        <v>0.6382505889070221</v>
       </c>
       <c r="F110">
-        <v>0.2702444605255197</v>
+        <v>0.2727586857531129</v>
       </c>
       <c r="G110">
-        <v>1.691262298122763</v>
+        <v>2.217710947271362</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.570282611941065</v>
+        <v>1.092186350504138</v>
       </c>
       <c r="C111">
-        <v>0.5609471468506405</v>
+        <v>0.5612107638781479</v>
       </c>
       <c r="D111">
-        <v>0.8044529922294413</v>
+        <v>0.1571272667669459</v>
       </c>
       <c r="E111">
-        <v>0.4211354072190877</v>
+        <v>0.8751445487165115</v>
       </c>
       <c r="F111">
-        <v>0.5229964543994291</v>
+        <v>0.3635743835188786</v>
       </c>
       <c r="G111">
-        <v>4.714730779955257</v>
+        <v>3.280954539982346</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.5735479178985873</v>
+        <v>1.003202463770772</v>
       </c>
       <c r="C112">
-        <v>0.5542421094271418</v>
+        <v>0.516892213793573</v>
       </c>
       <c r="D112">
-        <v>-1.003016160277661</v>
+        <v>0.006185712843092872</v>
       </c>
       <c r="E112">
-        <v>0.3158530641458727</v>
+        <v>0.9950645466992002</v>
       </c>
       <c r="F112">
-        <v>0.193552136088421</v>
+        <v>0.3642580346377462</v>
       </c>
       <c r="G112">
-        <v>1.69957935248788</v>
+        <v>2.762918282136522</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>1.891152517733873</v>
+        <v>1.421951210268179</v>
       </c>
       <c r="C113">
-        <v>0.3790494291153059</v>
+        <v>0.440961348308366</v>
       </c>
       <c r="D113">
-        <v>1.681011477712627</v>
+        <v>0.7983239835003065</v>
       </c>
       <c r="E113">
-        <v>0.09276068517920331</v>
+        <v>0.4246825036493833</v>
       </c>
       <c r="F113">
-        <v>0.8996614181787067</v>
+        <v>0.599152968044383</v>
       </c>
       <c r="G113">
-        <v>3.975337580410442</v>
+        <v>3.374672833521471</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,32 +7484,32 @@
         </is>
       </c>
       <c r="O113">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.6923907790862724</v>
+        <v>0.7606089797665178</v>
       </c>
       <c r="C114">
-        <v>0.6350220903140406</v>
+        <v>0.9586803593571707</v>
       </c>
       <c r="D114">
-        <v>-0.5788850162817634</v>
+        <v>-0.2854297313231141</v>
       </c>
       <c r="E114">
-        <v>0.5626667611120437</v>
+        <v>0.7753149321821452</v>
       </c>
       <c r="F114">
-        <v>0.1994433187637097</v>
+        <v>0.1161799665396671</v>
       </c>
       <c r="G114">
-        <v>2.403715471319798</v>
+        <v>4.979567797550859</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7547,32 +7547,32 @@
         </is>
       </c>
       <c r="O114">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B115">
-        <v>2.002987617479767</v>
+        <v>1.46149501917703</v>
       </c>
       <c r="C115">
-        <v>0.6620371984554552</v>
+        <v>0.940894041257944</v>
       </c>
       <c r="D115">
-        <v>1.049245988439992</v>
+        <v>0.4032971630204397</v>
       </c>
       <c r="E115">
-        <v>0.294064917568644</v>
+        <v>0.6867296285227749</v>
       </c>
       <c r="F115">
-        <v>0.5472064142901362</v>
+        <v>0.2311569096289358</v>
       </c>
       <c r="G115">
-        <v>7.331711198929915</v>
+        <v>9.240336767384646</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7610,32 +7610,32 @@
         </is>
       </c>
       <c r="O115">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B116">
-        <v>0.6234714564945798</v>
+        <v>1.63261185885281</v>
       </c>
       <c r="C116">
-        <v>0.6785045201922221</v>
+        <v>0.907227188878277</v>
       </c>
       <c r="D116">
-        <v>-0.6963141443118673</v>
+        <v>0.540306888727873</v>
       </c>
       <c r="E116">
-        <v>0.4862321171475855</v>
+        <v>0.588985408454737</v>
       </c>
       <c r="F116">
-        <v>0.1649196790379018</v>
+        <v>0.27583524878023</v>
       </c>
       <c r="G116">
-        <v>2.357005903304832</v>
+        <v>9.663092347528375</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7673,32 +7673,32 @@
         </is>
       </c>
       <c r="O116">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B117">
-        <v>2.799249245516424</v>
+        <v>2.261944295074632</v>
       </c>
       <c r="C117">
-        <v>0.5503255124836385</v>
+        <v>0.8432237671134089</v>
       </c>
       <c r="D117">
-        <v>1.870440732398574</v>
+        <v>0.9679811964753701</v>
       </c>
       <c r="E117">
-        <v>0.06142264005494341</v>
+        <v>0.3330537606843477</v>
       </c>
       <c r="F117">
-        <v>0.9519269982762428</v>
+        <v>0.4332399863750511</v>
       </c>
       <c r="G117">
-        <v>8.231509719456838</v>
+        <v>11.8096024257361</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7736,32 +7736,32 @@
         </is>
       </c>
       <c r="O117">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B118">
-        <v>0.5881666447684467</v>
+        <v>0.635660288536304</v>
       </c>
       <c r="C118">
-        <v>0.4912937207818869</v>
+        <v>0.5784702690700153</v>
       </c>
       <c r="D118">
-        <v>-1.080300723000423</v>
+        <v>-0.7832571872608598</v>
       </c>
       <c r="E118">
-        <v>0.2800082878671633</v>
+        <v>0.4334760987479141</v>
       </c>
       <c r="F118">
-        <v>0.2245486345423173</v>
+        <v>0.20456451236291</v>
       </c>
       <c r="G118">
-        <v>1.540601672877143</v>
+        <v>1.975239975667054</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7799,32 +7799,32 @@
         </is>
       </c>
       <c r="O118">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B119">
-        <v>1.912160841871162</v>
+        <v>1.315478172269966</v>
       </c>
       <c r="C119">
-        <v>0.5546779597353597</v>
+        <v>0.5886513260708227</v>
       </c>
       <c r="D119">
-        <v>1.168667191532102</v>
+        <v>0.4658109418789189</v>
       </c>
       <c r="E119">
-        <v>0.2425377453224722</v>
+        <v>0.6413508323050833</v>
       </c>
       <c r="F119">
-        <v>0.6447356503005898</v>
+        <v>0.4149757600749741</v>
       </c>
       <c r="G119">
-        <v>5.671098043796331</v>
+        <v>4.170081696834734</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7862,32 +7862,32 @@
         </is>
       </c>
       <c r="O119">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B120">
-        <v>0.4469638800413441</v>
+        <v>0.8656397953074373</v>
       </c>
       <c r="C120">
-        <v>0.564277834087186</v>
+        <v>0.550059850595526</v>
       </c>
       <c r="D120">
-        <v>-1.427093967305657</v>
+        <v>-0.2623103604896366</v>
       </c>
       <c r="E120">
-        <v>0.1535528111467923</v>
+        <v>0.7930821750973881</v>
       </c>
       <c r="F120">
-        <v>0.1478966255920435</v>
+        <v>0.2945272076618371</v>
       </c>
       <c r="G120">
-        <v>1.350786126876722</v>
+        <v>2.544186872135262</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7925,32 +7925,32 @@
         </is>
       </c>
       <c r="O120">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B121">
-        <v>2.283735174715706</v>
+        <v>1.783680182630505</v>
       </c>
       <c r="C121">
-        <v>0.3843480471173335</v>
+        <v>0.4810943760334653</v>
       </c>
       <c r="D121">
-        <v>2.148605523670771</v>
+        <v>1.202838314245557</v>
       </c>
       <c r="E121">
-        <v>0.0316656834566886</v>
+        <v>0.2290388949398316</v>
       </c>
       <c r="F121">
-        <v>1.075197114579251</v>
+        <v>0.6947182565071436</v>
       </c>
       <c r="G121">
-        <v>4.85068856446355</v>
+        <v>4.579575913125693</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.516580468314832</v>
+        <v>1.196862448579582</v>
       </c>
       <c r="C122">
-        <v>0.44901851674258</v>
+        <v>0.4328619997768319</v>
       </c>
       <c r="D122">
-        <v>0.9274853777138383</v>
+        <v>0.4151519574323378</v>
       </c>
       <c r="E122">
-        <v>0.3536745802848379</v>
+        <v>0.6780306659030307</v>
       </c>
       <c r="F122">
-        <v>0.6290138442386477</v>
+        <v>0.5123791383796596</v>
       </c>
       <c r="G122">
-        <v>3.656543235002964</v>
+        <v>2.795741695007269</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.7084465898206155</v>
+        <v>1.008373586149035</v>
       </c>
       <c r="C123">
-        <v>0.2682042037429943</v>
+        <v>0.2333370256346789</v>
       </c>
       <c r="D123">
-        <v>-1.285142450234847</v>
+        <v>0.03573681520551398</v>
       </c>
       <c r="E123">
-        <v>0.1987425098026777</v>
+        <v>0.9714922150012488</v>
       </c>
       <c r="F123">
-        <v>0.4188044445744696</v>
+        <v>0.6382702829643194</v>
       </c>
       <c r="G123">
-        <v>1.19840316197794</v>
+        <v>1.593082611524165</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>2.412709339909809</v>
+        <v>1.96234924346136</v>
       </c>
       <c r="C124">
-        <v>0.4179728741366591</v>
+        <v>0.4022122694736172</v>
       </c>
       <c r="D124">
-        <v>2.107194935329908</v>
+        <v>1.676085988096716</v>
       </c>
       <c r="E124">
-        <v>0.03510068577262248</v>
+        <v>0.09372135091921635</v>
       </c>
       <c r="F124">
-        <v>1.063471485825957</v>
+        <v>0.8920980658037791</v>
       </c>
       <c r="G124">
-        <v>5.473739951162824</v>
+        <v>4.316582112353079</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
         </is>
       </c>
       <c r="O124">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B125">
-        <v>1.195249736726738</v>
+        <v>0.8395261378638704</v>
       </c>
       <c r="C125">
-        <v>0.5439523522179367</v>
+        <v>0.8164101694987022</v>
       </c>
       <c r="D125">
-        <v>0.3278874473665674</v>
+        <v>-0.2142521914190056</v>
       </c>
       <c r="E125">
-        <v>0.7429967650942457</v>
+        <v>0.8303503980254523</v>
       </c>
       <c r="F125">
-        <v>0.4115717667012435</v>
+        <v>0.1694746032465335</v>
       </c>
       <c r="G125">
-        <v>3.47113686780746</v>
+        <v>4.158759617400332</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8240,32 +8240,32 @@
         </is>
       </c>
       <c r="O125">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B126">
-        <v>0.7224594916412652</v>
+        <v>0.9295436416840248</v>
       </c>
       <c r="C126">
-        <v>0.2765849888387839</v>
+        <v>0.3800142126630263</v>
       </c>
       <c r="D126">
-        <v>-1.175385290665051</v>
+        <v>-0.1922599700310899</v>
       </c>
       <c r="E126">
-        <v>0.2398406056187425</v>
+        <v>0.847538572692932</v>
       </c>
       <c r="F126">
-        <v>0.4201302300210355</v>
+        <v>0.4413682616511362</v>
       </c>
       <c r="G126">
-        <v>1.242347443164044</v>
+        <v>1.957665416545418</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8303,32 +8303,32 @@
         </is>
       </c>
       <c r="O126">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B127">
-        <v>1.935564478612772</v>
+        <v>1.791109464075199</v>
       </c>
       <c r="C127">
-        <v>0.5055860365352751</v>
+        <v>0.7787574623117841</v>
       </c>
       <c r="D127">
-        <v>1.306204990704721</v>
+        <v>0.7484168927905595</v>
       </c>
       <c r="E127">
-        <v>0.1914828561009196</v>
+        <v>0.4542087362983566</v>
       </c>
       <c r="F127">
-        <v>0.7185417855254292</v>
+        <v>0.3892625066578253</v>
       </c>
       <c r="G127">
-        <v>5.213906729346285</v>
+        <v>8.241413075828921</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8366,32 +8366,32 @@
         </is>
       </c>
       <c r="O127">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B128">
-        <v>1.274854067846248</v>
+        <v>0.9182045864183465</v>
       </c>
       <c r="C128">
-        <v>0.4670498857810613</v>
+        <v>0.6820943690443403</v>
       </c>
       <c r="D128">
-        <v>0.5199267205952981</v>
+        <v>-0.1251073986857147</v>
       </c>
       <c r="E128">
-        <v>0.6031146507147622</v>
+        <v>0.9004385260159893</v>
       </c>
       <c r="F128">
-        <v>0.5103955632681062</v>
+        <v>0.2411791044407273</v>
       </c>
       <c r="G128">
-        <v>3.184300592069204</v>
+        <v>3.495740912027844</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8429,32 +8429,32 @@
         </is>
       </c>
       <c r="O128">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B129">
-        <v>0.7208957863967617</v>
+        <v>0.9651847770467399</v>
       </c>
       <c r="C129">
-        <v>0.2630729444336086</v>
+        <v>0.3500414230422657</v>
       </c>
       <c r="D129">
-        <v>-1.243992206092654</v>
+        <v>-0.1012329251206569</v>
       </c>
       <c r="E129">
-        <v>0.2135024314248662</v>
+        <v>0.9193655604973686</v>
       </c>
       <c r="F129">
-        <v>0.4304714872969431</v>
+        <v>0.4860205852836408</v>
       </c>
       <c r="G129">
-        <v>1.207259366021885</v>
+        <v>1.916753491622367</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8492,32 +8492,32 @@
         </is>
       </c>
       <c r="O129">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B130">
-        <v>2.048077969264197</v>
+        <v>1.924329547209804</v>
       </c>
       <c r="C130">
-        <v>0.429509345395686</v>
+        <v>0.6429347025748673</v>
       </c>
       <c r="D130">
-        <v>1.669117994910959</v>
+        <v>1.018109019918279</v>
       </c>
       <c r="E130">
-        <v>0.09509399770245278</v>
+        <v>0.3086261492591078</v>
       </c>
       <c r="F130">
-        <v>0.8825665602699934</v>
+        <v>0.5457734906793977</v>
       </c>
       <c r="G130">
-        <v>4.75275583396469</v>
+        <v>6.784946996335443</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>1.147144829213285</v>
+        <v>0.9531458519420216</v>
       </c>
       <c r="C131">
-        <v>0.2854327257167794</v>
+        <v>0.2689123587530355</v>
       </c>
       <c r="D131">
-        <v>0.4809402904733307</v>
+        <v>-0.1784497454889098</v>
       </c>
       <c r="E131">
-        <v>0.6305589362937201</v>
+        <v>0.8583697849373016</v>
       </c>
       <c r="F131">
-        <v>0.6556279735509286</v>
+        <v>0.5626790524255513</v>
       </c>
       <c r="G131">
-        <v>2.0071462967993</v>
+        <v>1.614574082966213</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.7227485589303813</v>
+        <v>0.9516771020647854</v>
       </c>
       <c r="C132">
-        <v>0.2439102527028165</v>
+        <v>0.2115320174786762</v>
       </c>
       <c r="D132">
-        <v>-1.331202310521101</v>
+        <v>-0.2341464938430886</v>
       </c>
       <c r="E132">
-        <v>0.1831224513667173</v>
+        <v>0.8148712521106383</v>
       </c>
       <c r="F132">
-        <v>0.4480953641940846</v>
+        <v>0.6286852053099583</v>
       </c>
       <c r="G132">
-        <v>1.165746225416627</v>
+        <v>1.44060858907583</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>1.747330675068763</v>
+        <v>1.494384508933056</v>
       </c>
       <c r="C133">
-        <v>0.2444786308925243</v>
+        <v>0.2284379568861889</v>
       </c>
       <c r="D133">
-        <v>2.282773315884417</v>
+        <v>1.758527469937343</v>
       </c>
       <c r="E133">
-        <v>0.02244372455658838</v>
+        <v>0.07865780177640316</v>
       </c>
       <c r="F133">
-        <v>1.082117731187998</v>
+        <v>0.9550269243729739</v>
       </c>
       <c r="G133">
-        <v>2.821471638473529</v>
+        <v>2.338347750777074</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,32 +8744,32 @@
         </is>
       </c>
       <c r="O133">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B134">
-        <v>1.317564101925338</v>
+        <v>1.064417687938345</v>
       </c>
       <c r="C134">
-        <v>0.4402505795536955</v>
+        <v>0.6211328247035348</v>
       </c>
       <c r="D134">
-        <v>0.6264265563083632</v>
+        <v>0.1005064863027456</v>
       </c>
       <c r="E134">
-        <v>0.5310351954836772</v>
+        <v>0.9199422335896463</v>
       </c>
       <c r="F134">
-        <v>0.5559423786433969</v>
+        <v>0.3150669609520473</v>
       </c>
       <c r="G134">
-        <v>3.122581097196484</v>
+        <v>3.596013402904694</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8807,32 +8807,32 @@
         </is>
       </c>
       <c r="O134">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.7289523743988713</v>
+        <v>0.991193116407141</v>
       </c>
       <c r="C135">
-        <v>0.2639233197272466</v>
+        <v>0.3421106525314735</v>
       </c>
       <c r="D135">
-        <v>-1.197873986569296</v>
+        <v>-0.02585681951771251</v>
       </c>
       <c r="E135">
-        <v>0.2309660782879543</v>
+        <v>0.9793715415532914</v>
       </c>
       <c r="F135">
-        <v>0.4345574680678401</v>
+        <v>0.5069360329578452</v>
       </c>
       <c r="G135">
-        <v>1.222787785708467</v>
+        <v>1.938042928770459</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8870,32 +8870,32 @@
         </is>
       </c>
       <c r="O135">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B136">
-        <v>2.075855875948363</v>
+        <v>2.146999136000933</v>
       </c>
       <c r="C136">
-        <v>0.4071131364822199</v>
+        <v>0.5864560970985174</v>
       </c>
       <c r="D136">
-        <v>1.794030881164197</v>
+        <v>1.302861578650548</v>
       </c>
       <c r="E136">
-        <v>0.07280823996430127</v>
+        <v>0.1926220230939729</v>
       </c>
       <c r="F136">
-        <v>0.9346776708744702</v>
+        <v>0.6802045533128364</v>
       </c>
       <c r="G136">
-        <v>4.610335468566126</v>
+        <v>6.776792756735228</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8933,32 +8933,32 @@
         </is>
       </c>
       <c r="O136">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B137">
-        <v>1.195729561092453</v>
+        <v>0.9492402536208544</v>
       </c>
       <c r="C137">
-        <v>0.3235534354546803</v>
+        <v>0.3308033123938627</v>
       </c>
       <c r="D137">
-        <v>0.5524790989174844</v>
+        <v>-0.1574752894652544</v>
       </c>
       <c r="E137">
-        <v>0.5806201505506632</v>
+        <v>0.8748702810542698</v>
       </c>
       <c r="F137">
-        <v>0.6341964147406549</v>
+        <v>0.4963589494263365</v>
       </c>
       <c r="G137">
-        <v>2.254458003921438</v>
+        <v>1.815333560794208</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8996,32 +8996,32 @@
         </is>
       </c>
       <c r="O137">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.7024363674387921</v>
+        <v>0.9458436907202885</v>
       </c>
       <c r="C138">
-        <v>0.2460343338459395</v>
+        <v>0.2282788334836169</v>
       </c>
       <c r="D138">
-        <v>-1.435573875052474</v>
+        <v>-0.2439032762241052</v>
       </c>
       <c r="E138">
-        <v>0.1511236330621225</v>
+        <v>0.8073057317384007</v>
       </c>
       <c r="F138">
-        <v>0.4336927714987663</v>
+        <v>0.6046555950403075</v>
       </c>
       <c r="G138">
-        <v>1.137710570078084</v>
+        <v>1.479553475752986</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9059,32 +9059,32 @@
         </is>
       </c>
       <c r="O138">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B139">
-        <v>1.857338801407722</v>
+        <v>1.59137666487392</v>
       </c>
       <c r="C139">
-        <v>0.2759105825192169</v>
+        <v>0.2913551210434457</v>
       </c>
       <c r="D139">
-        <v>2.244004944057509</v>
+        <v>1.594615762788123</v>
       </c>
       <c r="E139">
-        <v>0.02483208324018685</v>
+        <v>0.1107981855217757</v>
       </c>
       <c r="F139">
-        <v>1.081522647051305</v>
+        <v>0.89902352636377</v>
       </c>
       <c r="G139">
-        <v>3.189676547800506</v>
+        <v>2.816922600177348</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.794375968508713</v>
+        <v>1.489617523126749</v>
       </c>
       <c r="C140">
-        <v>0.7448053035800715</v>
+        <v>0.8208962483032441</v>
       </c>
       <c r="D140">
-        <v>0.7849800596610506</v>
+        <v>0.4854686471536119</v>
       </c>
       <c r="E140">
-        <v>0.4324652599391254</v>
+        <v>0.6273439476576053</v>
       </c>
       <c r="F140">
-        <v>0.4168060560111897</v>
+        <v>0.2980757319803335</v>
       </c>
       <c r="G140">
-        <v>7.724900034262318</v>
+        <v>7.444283875322917</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.9676569283351159</v>
+        <v>1.79120456138344</v>
       </c>
       <c r="C141">
-        <v>0.5940852498796777</v>
+        <v>0.5967740890802801</v>
       </c>
       <c r="D141">
-        <v>-0.05534166587750152</v>
+        <v>0.9767319719748635</v>
       </c>
       <c r="E141">
-        <v>0.9558662684393968</v>
+        <v>0.3287018624096568</v>
       </c>
       <c r="F141">
-        <v>0.3020196006459393</v>
+        <v>0.5561221088264056</v>
       </c>
       <c r="G141">
-        <v>3.100328352704022</v>
+        <v>5.769261336312653</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>3.12399623816482</v>
+        <v>2.325639098130772</v>
       </c>
       <c r="C142">
-        <v>0.6775957965999925</v>
+        <v>0.7502034865176714</v>
       </c>
       <c r="D142">
-        <v>1.681109938284606</v>
+        <v>1.12502127402878</v>
       </c>
       <c r="E142">
-        <v>0.09274156236124206</v>
+        <v>0.260580019441776</v>
       </c>
       <c r="F142">
-        <v>0.8278276241965047</v>
+        <v>0.53452491685893</v>
       </c>
       <c r="G142">
-        <v>11.78911190060907</v>
+        <v>10.11851280299049</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,32 +9311,32 @@
         </is>
       </c>
       <c r="O142">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B143">
-        <v>1.93114825088191</v>
+        <v>1.293288661957293</v>
       </c>
       <c r="C143">
-        <v>0.8112199562449112</v>
+        <v>1.297592104659038</v>
       </c>
       <c r="D143">
-        <v>0.8112655138501104</v>
+        <v>0.1982042921834822</v>
       </c>
       <c r="E143">
-        <v>0.4172132099565121</v>
+        <v>0.8428852294299892</v>
       </c>
       <c r="F143">
-        <v>0.3938255937540218</v>
+        <v>0.1016677162720833</v>
       </c>
       <c r="G143">
-        <v>9.469505349653708</v>
+        <v>16.45158979150353</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9374,32 +9374,32 @@
         </is>
       </c>
       <c r="O143">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B144">
-        <v>0.7731185062283481</v>
+        <v>1.945733299913712</v>
       </c>
       <c r="C144">
-        <v>0.6404649674010925</v>
+        <v>0.9321472790118115</v>
       </c>
       <c r="D144">
-        <v>-0.4017751920079502</v>
+        <v>0.7140920098733243</v>
       </c>
       <c r="E144">
-        <v>0.687849481149045</v>
+        <v>0.475170286376215</v>
       </c>
       <c r="F144">
-        <v>0.2203338892528509</v>
+        <v>0.3130675893987634</v>
       </c>
       <c r="G144">
-        <v>2.712756656271016</v>
+        <v>12.09284577066493</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9437,32 +9437,32 @@
         </is>
       </c>
       <c r="O144">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B145">
-        <v>3.32470147032228</v>
+        <v>2.306886770887076</v>
       </c>
       <c r="C145">
-        <v>0.7474442748715306</v>
+        <v>1.220880495237211</v>
       </c>
       <c r="D145">
-        <v>1.607316996202588</v>
+        <v>0.6846688931266562</v>
       </c>
       <c r="E145">
-        <v>0.1079848477776347</v>
+        <v>0.4935528826219484</v>
       </c>
       <c r="F145">
-        <v>0.7682931042503502</v>
+        <v>0.2107710295412085</v>
       </c>
       <c r="G145">
-        <v>14.38726939707281</v>
+        <v>25.24885220363426</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9500,32 +9500,32 @@
         </is>
       </c>
       <c r="O145">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B146">
-        <v>1.835418873519735</v>
+        <v>1.430889024010653</v>
       </c>
       <c r="C146">
-        <v>0.717108595812089</v>
+        <v>1.151013687247878</v>
       </c>
       <c r="D146">
-        <v>0.8468350929715469</v>
+        <v>0.3112873028195814</v>
       </c>
       <c r="E146">
-        <v>0.3970870448680811</v>
+        <v>0.7555822190115532</v>
       </c>
       <c r="F146">
-        <v>0.4501230467419584</v>
+        <v>0.1499206047763032</v>
       </c>
       <c r="G146">
-        <v>7.484092329099648</v>
+        <v>13.65685125196203</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9563,32 +9563,32 @@
         </is>
       </c>
       <c r="O146">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B147">
-        <v>0.8164344063652006</v>
+        <v>1.921866568388445</v>
       </c>
       <c r="C147">
-        <v>0.5870950596294117</v>
+        <v>0.8506552006328411</v>
       </c>
       <c r="D147">
-        <v>-0.3454444073470628</v>
+        <v>0.7679925830549307</v>
       </c>
       <c r="E147">
-        <v>0.7297602972260314</v>
+        <v>0.442491591332839</v>
       </c>
       <c r="F147">
-        <v>0.258336087437559</v>
+        <v>0.3627807318634522</v>
       </c>
       <c r="G147">
-        <v>2.580224646539207</v>
+        <v>10.18127695954759</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9626,32 +9626,32 @@
         </is>
       </c>
       <c r="O147">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B148">
-        <v>3.053221389853518</v>
+        <v>2.573430234091158</v>
       </c>
       <c r="C148">
-        <v>0.6356172988758487</v>
+        <v>1.056510029465352</v>
       </c>
       <c r="D148">
-        <v>1.756083776524348</v>
+        <v>0.8946812657073033</v>
       </c>
       <c r="E148">
-        <v>0.07907410483774135</v>
+        <v>0.3709574961511512</v>
       </c>
       <c r="F148">
-        <v>0.8784557108728624</v>
+        <v>0.3244960625976991</v>
       </c>
       <c r="G148">
-        <v>10.61198730917947</v>
+        <v>20.40870116179163</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>1.191367523821983</v>
+        <v>0.9215873831593193</v>
       </c>
       <c r="C149">
-        <v>0.4576602780893196</v>
+        <v>0.4338036831291346</v>
       </c>
       <c r="D149">
-        <v>0.3826021950938686</v>
+        <v>-0.1882364822112896</v>
       </c>
       <c r="E149">
-        <v>0.7020147424380918</v>
+        <v>0.8506912749573797</v>
       </c>
       <c r="F149">
-        <v>0.4858303280846046</v>
+        <v>0.3938058433267694</v>
       </c>
       <c r="G149">
-        <v>2.921506737575571</v>
+        <v>2.15670569441931</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.7083511090640268</v>
+        <v>1.144404422151683</v>
       </c>
       <c r="C150">
-        <v>0.4894626048556321</v>
+        <v>0.4344189620841836</v>
       </c>
       <c r="D150">
-        <v>-0.7044774984579202</v>
+        <v>0.3104936895602452</v>
       </c>
       <c r="E150">
-        <v>0.4811354582276592</v>
+        <v>0.7561855575344267</v>
       </c>
       <c r="F150">
-        <v>0.2714046308909665</v>
+        <v>0.4884289938532026</v>
       </c>
       <c r="G150">
-        <v>1.848757304048409</v>
+        <v>2.681375385004163</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.636131496931199</v>
+        <v>1.238370145414619</v>
       </c>
       <c r="C151">
-        <v>0.3384872276574247</v>
+        <v>0.3341273540139086</v>
       </c>
       <c r="D151">
-        <v>1.454514592633551</v>
+        <v>0.6398641524243531</v>
       </c>
       <c r="E151">
-        <v>0.1458036907071827</v>
+        <v>0.5222609210658677</v>
       </c>
       <c r="F151">
-        <v>0.8427472707420298</v>
+        <v>0.6433402954035786</v>
       </c>
       <c r="G151">
-        <v>3.176428293731905</v>
+        <v>2.38374718327288</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,32 +9878,32 @@
         </is>
       </c>
       <c r="O151">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B152">
-        <v>1.812833094065653</v>
+        <v>1.337588394987577</v>
       </c>
       <c r="C152">
-        <v>0.642016869683087</v>
+        <v>0.8915411058069684</v>
       </c>
       <c r="D152">
-        <v>0.9265969400333961</v>
+        <v>0.326253366692787</v>
       </c>
       <c r="E152">
-        <v>0.354135844259633</v>
+        <v>0.7442326674918756</v>
       </c>
       <c r="F152">
-        <v>0.515076896873176</v>
+        <v>0.2330458250303698</v>
       </c>
       <c r="G152">
-        <v>6.380336308791634</v>
+        <v>7.67721418812067</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9941,32 +9941,32 @@
         </is>
       </c>
       <c r="O152">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B153">
-        <v>0.7628573337829074</v>
+        <v>1.892238397628838</v>
       </c>
       <c r="C153">
-        <v>0.579270804819612</v>
+        <v>0.7455799366868049</v>
       </c>
       <c r="D153">
-        <v>-0.4672844610049254</v>
+        <v>0.855388449025493</v>
       </c>
       <c r="E153">
-        <v>0.6402963723965411</v>
+        <v>0.3923361361410533</v>
       </c>
       <c r="F153">
-        <v>0.2451134386867133</v>
+        <v>0.4388711759490416</v>
       </c>
       <c r="G153">
-        <v>2.374212180386304</v>
+        <v>8.158581264121798</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10004,32 +10004,32 @@
         </is>
       </c>
       <c r="O153">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B154">
-        <v>2.757181391858742</v>
+        <v>2.075075458858537</v>
       </c>
       <c r="C154">
-        <v>0.5484435483185643</v>
+        <v>0.7924805114655064</v>
       </c>
       <c r="D154">
-        <v>1.849249437228455</v>
+        <v>0.9211551680765545</v>
       </c>
       <c r="E154">
-        <v>0.0644218031445549</v>
+        <v>0.3569694208319979</v>
       </c>
       <c r="F154">
-        <v>0.9410860680016369</v>
+        <v>0.4390088344024509</v>
       </c>
       <c r="G154">
-        <v>8.077953213944388</v>
+        <v>9.80831778890718</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10067,32 +10067,32 @@
         </is>
       </c>
       <c r="O154">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B155">
-        <v>1.449200690289223</v>
+        <v>1.0291997772324</v>
       </c>
       <c r="C155">
-        <v>0.4943994201162176</v>
+        <v>0.5047627104827682</v>
       </c>
       <c r="D155">
-        <v>0.7504299990396248</v>
+        <v>0.05702003016538881</v>
       </c>
       <c r="E155">
-        <v>0.45299576890403</v>
+        <v>0.9545292393334565</v>
       </c>
       <c r="F155">
-        <v>0.549914261525843</v>
+        <v>0.3826880363128019</v>
       </c>
       <c r="G155">
-        <v>3.819109246062101</v>
+        <v>2.767926041433418</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10130,32 +10130,32 @@
         </is>
       </c>
       <c r="O155">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B156">
-        <v>0.5836216182613702</v>
+        <v>1.08193226753109</v>
       </c>
       <c r="C156">
-        <v>0.501287167576025</v>
+        <v>0.4692533012015191</v>
       </c>
       <c r="D156">
-        <v>-1.074239387935644</v>
+        <v>0.1678167824049804</v>
       </c>
       <c r="E156">
-        <v>0.2827154031330475</v>
+        <v>0.8667274192911339</v>
       </c>
       <c r="F156">
-        <v>0.2184917080842033</v>
+        <v>0.4312915399123862</v>
       </c>
       <c r="G156">
-        <v>1.558934186970396</v>
+        <v>2.7141210137411</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10193,32 +10193,32 @@
         </is>
       </c>
       <c r="O156">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B157">
-        <v>2.006678848630579</v>
+        <v>1.441234777846233</v>
       </c>
       <c r="C157">
-        <v>0.3636300922726926</v>
+        <v>0.4018767904039903</v>
       </c>
       <c r="D157">
-        <v>1.915355896502716</v>
+        <v>0.9094833030940217</v>
       </c>
       <c r="E157">
-        <v>0.05544713160308939</v>
+        <v>0.3630950674349654</v>
       </c>
       <c r="F157">
-        <v>0.9839100062561187</v>
+        <v>0.6556266359114094</v>
       </c>
       <c r="G157">
-        <v>4.092610071995905</v>
+        <v>3.168202100248647</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
   </sheetData>
